--- a/doc/Java.xlsx
+++ b/doc/Java.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10814"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11014"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hades/Documents/Gitee/JavaAboutDemos/doc/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hades/Documents/GitHub/JavaAboutDemos/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF32C83-0173-8647-A85B-B11823B9AA58}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B5F7051-4AC1-F345-B6DA-0A7B55BE834E}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{7C69AD57-AE32-C847-879F-875651E96C78}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{7C69AD57-AE32-C847-879F-875651E96C78}"/>
   </bookViews>
   <sheets>
     <sheet name="Object References" sheetId="1" r:id="rId1"/>
+    <sheet name="LRU" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Usage</t>
   </si>
@@ -101,6 +102,9 @@
       </rPr>
       <t>PhantomReference: the weakest and most enigmatic reference, that get() method will always return null – you can never access the Object it references (even when the Object still exists, and has other references). Realistically, you should probably never be using these.4</t>
     </r>
+  </si>
+  <si>
+    <t>get(2)</t>
   </si>
 </sst>
 </file>
@@ -136,10 +140,39 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -148,12 +181,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -169,6 +215,191 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>393700</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Right Arrow 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{173F8953-51F4-8543-8F35-5BEBF6A9C7EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2260600" y="876300"/>
+          <a:ext cx="609600" cy="76200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent4"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>431800</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Down Arrow 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01FCC782-9969-B841-9A74-6986049708B5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1092200" y="114300"/>
+          <a:ext cx="165100" cy="444500"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Down Arrow 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16AB0841-E825-E847-9E14-BE72A08C8162}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3632200" y="165100"/>
+          <a:ext cx="165100" cy="444500"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -550,4 +781,62 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1661C7ED-FEB2-6A4E-A2BB-13A4AD95C604}">
+  <dimension ref="B3:E7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="2" max="2" width="10.83203125" style="5"/>
+    <col min="5" max="5" width="10.83203125" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:5">
+      <c r="B3" s="4"/>
+      <c r="C3" s="3"/>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="2:5">
+      <c r="B4" s="4"/>
+      <c r="C4" s="3"/>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="2:5">
+      <c r="B5" s="4">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="E5" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
+      <c r="B6" s="4">
+        <v>2</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="B7" s="4">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C6:D6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/doc/Java.xlsx
+++ b/doc/Java.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hades/Documents/GitHub/JavaAboutDemos/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B5F7051-4AC1-F345-B6DA-0A7B55BE834E}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4FF14D-3852-7647-900E-242F20903478}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{7C69AD57-AE32-C847-879F-875651E96C78}"/>
   </bookViews>
@@ -344,13 +344,13 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>330200</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -365,7 +365,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3632200" y="165100"/>
+          <a:off x="3632200" y="127000"/>
           <a:ext cx="165100" cy="444500"/>
         </a:xfrm>
         <a:prstGeom prst="downArrow">

--- a/doc/Java.xlsx
+++ b/doc/Java.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hades/Documents/GitHub/JavaAboutDemos/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4FF14D-3852-7647-900E-242F20903478}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2DB498E-0A2B-0A4C-8687-734EA25CEFE2}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{7C69AD57-AE32-C847-879F-875651E96C78}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="2" xr2:uid="{7C69AD57-AE32-C847-879F-875651E96C78}"/>
   </bookViews>
   <sheets>
     <sheet name="Object References" sheetId="1" r:id="rId1"/>
     <sheet name="LRU" sheetId="2" r:id="rId2"/>
+    <sheet name="Java 知识坐标系" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>Usage</t>
   </si>
@@ -106,12 +107,99 @@
   <si>
     <t>get(2)</t>
   </si>
+  <si>
+    <t>面向对象</t>
+  </si>
+  <si>
+    <t>面向过程</t>
+  </si>
+  <si>
+    <t>算法</t>
+  </si>
+  <si>
+    <t>数据结构</t>
+  </si>
+  <si>
+    <t>操作符</t>
+  </si>
+  <si>
+    <t>对象</t>
+  </si>
+  <si>
+    <t>控制执行流程</t>
+  </si>
+  <si>
+    <t>构造</t>
+  </si>
+  <si>
+    <t>析构</t>
+  </si>
+  <si>
+    <t>访问控制权限</t>
+  </si>
+  <si>
+    <t>组合</t>
+  </si>
+  <si>
+    <t>继承</t>
+  </si>
+  <si>
+    <t>多态</t>
+  </si>
+  <si>
+    <t>接口</t>
+  </si>
+  <si>
+    <t>内部类</t>
+  </si>
+  <si>
+    <t>容器</t>
+  </si>
+  <si>
+    <t>异常处理</t>
+  </si>
+  <si>
+    <t>字符串</t>
+  </si>
+  <si>
+    <t>变量</t>
+  </si>
+  <si>
+    <t>类型信息</t>
+  </si>
+  <si>
+    <t>(静态)</t>
+  </si>
+  <si>
+    <t>(动态)</t>
+  </si>
+  <si>
+    <t>泛型</t>
+  </si>
+  <si>
+    <t>数组</t>
+  </si>
+  <si>
+    <t>I/O</t>
+  </si>
+  <si>
+    <t>枚举类型</t>
+  </si>
+  <si>
+    <t>注解</t>
+  </si>
+  <si>
+    <t>并发</t>
+  </si>
+  <si>
+    <t>图形化界面</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -131,13 +219,26 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri (Body)_x0000_"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -181,7 +282,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -200,6 +301,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -397,6 +501,217 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Arrow Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC1C41DA-B823-C54E-AF0F-508B6129CBAE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="850900" y="3467100"/>
+          <a:ext cx="7747000" cy="12700"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>800100</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="Straight Arrow Connector 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{103A12ED-DDD3-E241-8B25-6CDBBE7DFD6B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="800100" y="0"/>
+          <a:ext cx="38100" cy="3479800"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>812800</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="Straight Connector 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE15DF8E-04AD-D84F-8565-D67075C81CEC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4114800" y="88900"/>
+          <a:ext cx="12700" cy="3365500"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>812800</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>546100</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="Straight Connector 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2DAEEB2-1FB9-4441-81D9-33B2330E878C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="812800" y="1397000"/>
+          <a:ext cx="7162800" cy="50800"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -839,4 +1154,272 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6601D41D-AD5A-BE45-B683-D4A75B94E650}">
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" s="9"/>
+      <c r="C4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="B5" s="9"/>
+      <c r="C5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="B9" s="9"/>
+      <c r="C9" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="9"/>
+      <c r="C10" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="9"/>
+      <c r="C12" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+    </row>
+    <row r="17" spans="2:10">
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+    </row>
+    <row r="18" spans="2:10">
+      <c r="D18" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10">
+      <c r="D19" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/doc/Java.xlsx
+++ b/doc/Java.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hades/Documents/GitHub/JavaAboutDemos/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2DB498E-0A2B-0A4C-8687-734EA25CEFE2}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F9E9C86-C8C8-2748-9360-1DD33BEB60B2}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="2" xr2:uid="{7C69AD57-AE32-C847-879F-875651E96C78}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>Usage</t>
   </si>
@@ -194,12 +194,21 @@
   <si>
     <t>图形化界面</t>
   </si>
+  <si>
+    <t>新东西</t>
+  </si>
+  <si>
+    <t>其他语言里中类似基本概念</t>
+  </si>
+  <si>
+    <t>封装</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -226,8 +235,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -237,6 +252,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FA00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -282,7 +309,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -304,12 +331,21 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF00FA00"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1158,31 +1194,37 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6601D41D-AD5A-BE45-B683-D4A75B94E650}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
+      <c r="C1" s="14" t="s">
+        <v>47</v>
+      </c>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
       <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="G1" s="14" t="s">
+        <v>49</v>
+      </c>
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
     </row>
     <row r="2" spans="1:10">
       <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
+      <c r="C2" s="11" t="s">
+        <v>35</v>
+      </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="9" t="s">
-        <v>49</v>
+      <c r="H2" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
@@ -1192,15 +1234,12 @@
         <v>21</v>
       </c>
       <c r="B3" s="9"/>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="11" t="s">
         <v>32</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>35</v>
       </c>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="11" t="s">
         <v>34</v>
       </c>
       <c r="H3" s="9"/>
@@ -1209,15 +1248,12 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="9"/>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="11" t="s">
         <v>30</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>47</v>
       </c>
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="11" t="s">
         <v>36</v>
       </c>
       <c r="H4" s="9"/>
@@ -1226,13 +1262,13 @@
     </row>
     <row r="5" spans="1:10">
       <c r="B5" s="9"/>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="11" t="s">
         <v>29</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="11" t="s">
         <v>40</v>
       </c>
       <c r="H5" s="9"/>
@@ -1241,13 +1277,13 @@
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="9"/>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="11" t="s">
         <v>28</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="11" t="s">
         <v>43</v>
       </c>
       <c r="H6" s="9"/>
@@ -1256,13 +1292,13 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="9"/>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="11" t="s">
         <v>26</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="11" t="s">
         <v>48</v>
       </c>
       <c r="H7" s="9"/>
@@ -1282,13 +1318,13 @@
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="9"/>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="11" t="s">
         <v>37</v>
       </c>
       <c r="H9" s="9"/>
@@ -1297,13 +1333,13 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="9"/>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="11" t="s">
         <v>27</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="11" t="s">
         <v>39</v>
       </c>
       <c r="H10" s="9"/>
@@ -1315,13 +1351,13 @@
         <v>22</v>
       </c>
       <c r="B11" s="9"/>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="11" t="s">
         <v>31</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="11" t="s">
         <v>44</v>
       </c>
       <c r="H11" s="9"/>
@@ -1330,13 +1366,13 @@
     </row>
     <row r="12" spans="1:10">
       <c r="B12" s="9"/>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="14" t="s">
         <v>45</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="11" t="s">
         <v>38</v>
       </c>
       <c r="H12" s="9"/>
@@ -1349,7 +1385,7 @@
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="11" t="s">
         <v>46</v>
       </c>
       <c r="H13" s="9"/>
@@ -1418,6 +1454,16 @@
         <v>42</v>
       </c>
     </row>
+    <row r="22" spans="2:10">
+      <c r="B22" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10">
+      <c r="B23" s="13" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/doc/Java.xlsx
+++ b/doc/Java.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hades/Documents/GitHub/JavaAboutDemos/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F9E9C86-C8C8-2748-9360-1DD33BEB60B2}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD145AD4-90C0-CA4C-A225-D48EBB7079A8}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="2" xr2:uid="{7C69AD57-AE32-C847-879F-875651E96C78}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>Usage</t>
   </si>
@@ -202,6 +202,15 @@
   </si>
   <si>
     <t>封装</t>
+  </si>
+  <si>
+    <t>原子类型</t>
+  </si>
+  <si>
+    <t>类</t>
+  </si>
+  <si>
+    <t>抽象</t>
   </si>
 </sst>
 </file>
@@ -322,12 +331,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -335,6 +338,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1166,10 +1175,10 @@
       <c r="B6" s="4">
         <v>2</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="7"/>
+      <c r="D6" s="14"/>
       <c r="E6" s="4">
         <v>3</v>
       </c>
@@ -1198,269 +1207,276 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="B1" s="9"/>
-      <c r="C1" s="14" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="14" t="s">
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="B2" s="9"/>
-      <c r="C2" s="11" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="11" t="s">
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="7"/>
+      <c r="C3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="11" t="s">
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
+      <c r="H3" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="B4" s="9"/>
-      <c r="C4" s="11" t="s">
+      <c r="B4" s="7"/>
+      <c r="C4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="11" t="s">
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
+      <c r="H4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="B5" s="9"/>
-      <c r="C5" s="11" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="11" t="s">
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="B6" s="9"/>
-      <c r="C6" s="11" t="s">
+      <c r="B6" s="7"/>
+      <c r="C6" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="11" t="s">
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="B7" s="9"/>
-      <c r="C7" s="11" t="s">
+      <c r="B7" s="7"/>
+      <c r="C7" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="11" t="s">
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="B9" s="9"/>
-      <c r="C9" s="11" t="s">
+      <c r="B9" s="7"/>
+      <c r="C9" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="11" t="s">
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="B10" s="9"/>
-      <c r="C10" s="11" t="s">
+      <c r="B10" s="7"/>
+      <c r="C10" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="11" t="s">
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="11" t="s">
+      <c r="B11" s="7"/>
+      <c r="C11" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="11" t="s">
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="B12" s="9"/>
-      <c r="C12" s="14" t="s">
+      <c r="B12" s="7"/>
+      <c r="C12" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="11" t="s">
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="11" t="s">
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
     </row>
     <row r="17" spans="2:10">
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
     </row>
     <row r="18" spans="2:10">
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="19" spans="2:10">
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10" t="s">
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="22" spans="2:10">
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="10" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="23" spans="2:10">
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="11" t="s">
         <v>50</v>
       </c>
     </row>

--- a/doc/Java.xlsx
+++ b/doc/Java.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hades/Documents/GitHub/JavaAboutDemos/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD145AD4-90C0-CA4C-A225-D48EBB7079A8}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05FD973A-7C44-E945-959A-A817BFC782CC}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="2" xr2:uid="{7C69AD57-AE32-C847-879F-875651E96C78}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="28800" windowHeight="17540" xr2:uid="{7C69AD57-AE32-C847-879F-875651E96C78}"/>
   </bookViews>
   <sheets>
-    <sheet name="Object References" sheetId="1" r:id="rId1"/>
-    <sheet name="LRU" sheetId="2" r:id="rId2"/>
-    <sheet name="Java 知识坐标系" sheetId="3" r:id="rId3"/>
+    <sheet name="JavaReadUnsigned8Bytes" sheetId="4" r:id="rId1"/>
+    <sheet name="Object References" sheetId="1" r:id="rId2"/>
+    <sheet name="LRU" sheetId="2" r:id="rId3"/>
+    <sheet name="Java 知识坐标系" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t>Usage</t>
   </si>
@@ -212,12 +213,45 @@
   <si>
     <t>抽象</t>
   </si>
+  <si>
+    <t>int num = 183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp; 0xFF </t>
+  </si>
+  <si>
+    <t>web: Unsigned byte = 183,  and java signed byte = -73</t>
+  </si>
+  <si>
+    <t>java: signed 8 byte, [-128,127]</t>
+  </si>
+  <si>
+    <t>+/-</t>
+  </si>
+  <si>
+    <t>web: Unsigned 8 byte, [0,255]</t>
+  </si>
+  <si>
+    <t>https://developer.mozilla.org/zh-CN/docs/Web/JavaScript/Reference/Global_Objects/Uint8Array</t>
+  </si>
+  <si>
+    <t>https://developer.mozilla.org/zh-CN/docs/Web/JavaScript/Reference/Operators/Bitwise_Operators</t>
+  </si>
+  <si>
+    <t>https://docs.oracle.com/javase/tutorial/java/nutsandbolts/datatypes.html</t>
+  </si>
+  <si>
+    <t>JavaScript 8 Unsigned Bytes -&gt; Java signed bytes -&gt; int[]/short[]</t>
+  </si>
+  <si>
+    <t>https://www.tutorialspoint.com/cplusplus/cpp_data_types.htm</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -250,6 +284,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -277,7 +326,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -314,11 +363,56 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFF00FF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFF00FF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFF00FF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFF00FF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -338,15 +432,38 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{2558BA20-FF6B-5F4A-ABF4-5CBF79168B2D}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1058,6 +1175,272 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{980B7C82-C9EB-E845-BC6F-23EE073ABA64}">
+  <dimension ref="B5:AE16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="3.6640625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="10" width="3.6640625" style="13"/>
+    <col min="11" max="11" width="4" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="19" width="3.6640625" style="13"/>
+    <col min="20" max="20" width="3.6640625" style="14"/>
+    <col min="21" max="21" width="3.83203125" style="14" customWidth="1"/>
+    <col min="22" max="31" width="3.6640625" style="14"/>
+    <col min="32" max="16384" width="3.6640625" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="2:21">
+      <c r="B5" s="13">
+        <v>16</v>
+      </c>
+      <c r="C5" s="13">
+        <v>15</v>
+      </c>
+      <c r="D5" s="13">
+        <v>14</v>
+      </c>
+      <c r="E5" s="13">
+        <v>13</v>
+      </c>
+      <c r="F5" s="13">
+        <v>12</v>
+      </c>
+      <c r="G5" s="13">
+        <v>11</v>
+      </c>
+      <c r="H5" s="13">
+        <v>10</v>
+      </c>
+      <c r="I5" s="13">
+        <v>9</v>
+      </c>
+      <c r="K5" s="13">
+        <v>8</v>
+      </c>
+      <c r="L5" s="13">
+        <v>7</v>
+      </c>
+      <c r="M5" s="13">
+        <v>6</v>
+      </c>
+      <c r="N5" s="13">
+        <v>5</v>
+      </c>
+      <c r="O5" s="13">
+        <v>4</v>
+      </c>
+      <c r="P5" s="13">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="13">
+        <v>2</v>
+      </c>
+      <c r="R5" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21">
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="K6" s="16">
+        <v>128</v>
+      </c>
+      <c r="L6" s="16">
+        <v>64</v>
+      </c>
+      <c r="M6" s="16">
+        <v>32</v>
+      </c>
+      <c r="N6" s="16">
+        <v>16</v>
+      </c>
+      <c r="O6" s="16">
+        <v>8</v>
+      </c>
+      <c r="P6" s="16">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>2</v>
+      </c>
+      <c r="R6" s="16">
+        <v>1</v>
+      </c>
+      <c r="U6" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="2:21">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="K7" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="L7" s="16">
+        <v>64</v>
+      </c>
+      <c r="M7" s="16">
+        <v>32</v>
+      </c>
+      <c r="N7" s="16">
+        <v>16</v>
+      </c>
+      <c r="O7" s="16">
+        <v>8</v>
+      </c>
+      <c r="P7" s="16">
+        <v>4</v>
+      </c>
+      <c r="Q7" s="16">
+        <v>2</v>
+      </c>
+      <c r="R7" s="16">
+        <v>1</v>
+      </c>
+      <c r="U7" s="14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="2:21">
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="K8" s="15">
+        <v>1</v>
+      </c>
+      <c r="L8" s="15">
+        <v>0</v>
+      </c>
+      <c r="M8" s="15">
+        <v>1</v>
+      </c>
+      <c r="N8" s="15">
+        <v>1</v>
+      </c>
+      <c r="O8" s="15">
+        <v>0</v>
+      </c>
+      <c r="P8" s="15">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="15">
+        <v>1</v>
+      </c>
+      <c r="R8" s="15">
+        <v>1</v>
+      </c>
+      <c r="U8" s="14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="2:21">
+      <c r="K9" s="13">
+        <v>1</v>
+      </c>
+      <c r="L9" s="13">
+        <v>1</v>
+      </c>
+      <c r="M9" s="13">
+        <v>1</v>
+      </c>
+      <c r="N9" s="13">
+        <v>1</v>
+      </c>
+      <c r="O9" s="13">
+        <v>1</v>
+      </c>
+      <c r="P9" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="13">
+        <v>1</v>
+      </c>
+      <c r="R9" s="13">
+        <v>1</v>
+      </c>
+      <c r="U9" s="14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="2:21">
+      <c r="K10" s="13">
+        <v>1</v>
+      </c>
+      <c r="L10" s="13">
+        <v>0</v>
+      </c>
+      <c r="M10" s="13">
+        <v>1</v>
+      </c>
+      <c r="N10" s="13">
+        <v>1</v>
+      </c>
+      <c r="O10" s="13">
+        <v>0</v>
+      </c>
+      <c r="P10" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="13">
+        <v>1</v>
+      </c>
+      <c r="R10" s="13">
+        <v>1</v>
+      </c>
+      <c r="U10" s="14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="2:21">
+      <c r="U12" s="14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="2:21">
+      <c r="U13" s="14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="2:21" ht="16">
+      <c r="U14" s="21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="2:21">
+      <c r="U15" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="2:21">
+      <c r="U16" s="14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="U14" r:id="rId1" xr:uid="{99704F72-9D01-1444-9468-4E615C52D4F3}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98ED4665-8CA5-BC48-874C-AC7F75724267}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -1143,7 +1526,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1661C7ED-FEB2-6A4E-A2BB-13A4AD95C604}">
   <dimension ref="B3:E7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
@@ -1175,10 +1558,10 @@
       <c r="B6" s="4">
         <v>2</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="14"/>
+      <c r="D6" s="20"/>
       <c r="E6" s="4">
         <v>3</v>
       </c>
@@ -1201,7 +1584,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6601D41D-AD5A-BE45-B683-D4A75B94E650}">
   <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>

--- a/doc/Java.xlsx
+++ b/doc/Java.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11014"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hades/Documents/GitHub/JavaAboutDemos/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05FD973A-7C44-E945-959A-A817BFC782CC}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF64B1D7-E75A-C44D-A4A1-7311FA4477FE}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="28800" windowHeight="17540" xr2:uid="{7C69AD57-AE32-C847-879F-875651E96C78}"/>
+    <workbookView xWindow="960" yWindow="460" windowWidth="27840" windowHeight="17540" activeTab="5" xr2:uid="{7C69AD57-AE32-C847-879F-875651E96C78}"/>
   </bookViews>
   <sheets>
-    <sheet name="JavaReadUnsigned8Bytes" sheetId="4" r:id="rId1"/>
-    <sheet name="Object References" sheetId="1" r:id="rId2"/>
-    <sheet name="LRU" sheetId="2" r:id="rId3"/>
-    <sheet name="Java 知识坐标系" sheetId="3" r:id="rId4"/>
+    <sheet name="Readme" sheetId="6" r:id="rId1"/>
+    <sheet name="JavaReadUnsigned8Bytes" sheetId="4" r:id="rId2"/>
+    <sheet name="ObjectReferences" sheetId="1" r:id="rId3"/>
+    <sheet name="LRU" sheetId="2" r:id="rId4"/>
+    <sheet name="Java知识坐标系" sheetId="3" r:id="rId5"/>
+    <sheet name="引用与对象" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="84">
   <si>
     <t>Usage</t>
   </si>
@@ -246,23 +248,86 @@
   <si>
     <t>https://www.tutorialspoint.com/cplusplus/cpp_data_types.htm</t>
   </si>
+  <si>
+    <t>JavaReadUnsigned8Bytes</t>
+  </si>
+  <si>
+    <t>Page</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Link</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>JavaReadUnsigned8Bytes</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>LRU</t>
+  </si>
+  <si>
+    <t>LRU</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Home</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ObjectReferences</t>
+  </si>
+  <si>
+    <t>ObjectReferences</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Java知识坐标系</t>
+  </si>
+  <si>
+    <t>Java知识坐标系</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>引用与对象</t>
+  </si>
+  <si>
+    <t>引用与对象</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>引用</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>对象</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>指向</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>操纵</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -274,20 +339,20 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -295,12 +360,37 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -322,6 +412,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -412,7 +508,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -450,14 +546,29 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -672,15 +783,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -725,15 +836,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -778,15 +889,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>812800</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>88900</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -828,15 +939,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>812800</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>177800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>546100</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -874,6 +985,234 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>241300</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78F038D8-C58F-B847-A471-46239678CF4F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1066800" y="1638300"/>
+          <a:ext cx="2235200" cy="2235200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>219724</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>558799</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Picture 15" descr="Clipart - TV VINTAGE">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C77EB1A-6C77-3247-917B-F980EDD505DF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+            <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
+              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8474724" y="1638300"/>
+          <a:ext cx="2815575" cy="2946400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="Right Arrow 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3B4182C-38A3-6447-841D-F0082F03688A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3530600" y="2705100"/>
+          <a:ext cx="5232400" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>317500</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>596900</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>304800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="Right Arrow 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9FD76C24-1175-6543-89B8-DEF2FFA9225D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3619500" y="1295400"/>
+          <a:ext cx="5232400" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1175,11 +1514,82 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DB7D6FA-3CC5-D149-87C6-B74F2C3A7F2D}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B2" location="JavaReadUnsigned8Bytes!A1" display="JavaReadUnsigned8Bytes" xr:uid="{B1FBB091-68F0-464C-BCDC-3C856985EDAA}"/>
+    <hyperlink ref="B3" location="ObjectReferences!A1" display="ObjectReferences" xr:uid="{A0F24EBA-848A-1942-926B-4CB0FA4EF4E4}"/>
+    <hyperlink ref="B4" location="LRU!A1" display="LRU" xr:uid="{A09283A5-69D6-CA40-964D-B15873694DBF}"/>
+    <hyperlink ref="B5" location="Java知识坐标系!A1" display="Java知识坐标系" xr:uid="{87E8B54B-C023-8741-BABD-4BA61CF4F9AB}"/>
+    <hyperlink ref="B6" location="引用与对象!A1" display="引用与对象" xr:uid="{ED9556B9-9183-3049-9D57-16682A24BDD4}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{980B7C82-C9EB-E845-BC6F-23EE073ABA64}">
-  <dimension ref="B5:AE16"/>
+  <dimension ref="A1:AE16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="3.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="10" width="3.6640625" style="13"/>
+    <col min="1" max="1" width="6.83203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="3.6640625" style="13"/>
     <col min="11" max="11" width="4" style="13" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="3.6640625" style="13"/>
     <col min="20" max="20" width="3.6640625" style="14"/>
@@ -1188,7 +1598,17 @@
     <col min="32" max="16384" width="3.6640625" style="13"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:21">
+    <row r="1" spans="1:21" ht="16">
+      <c r="A1" s="25" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
+      <c r="B2" s="22" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
       <c r="B5" s="13">
         <v>16</v>
       </c>
@@ -1238,7 +1658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:21">
+    <row r="6" spans="1:21">
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
@@ -1275,7 +1695,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="2:21">
+    <row r="7" spans="1:21">
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -1312,7 +1732,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="2:21">
+    <row r="8" spans="1:21">
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
@@ -1349,7 +1769,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="2:21">
+    <row r="9" spans="1:21">
       <c r="K9" s="13">
         <v>1</v>
       </c>
@@ -1378,7 +1798,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="2:21">
+    <row r="10" spans="1:21">
       <c r="K10" s="13">
         <v>1</v>
       </c>
@@ -1407,145 +1827,162 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="2:21">
+    <row r="12" spans="1:21">
       <c r="U12" s="14" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="2:21">
+    <row r="13" spans="1:21">
       <c r="U13" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="2:21" ht="16">
-      <c r="U14" s="21" t="s">
+    <row r="14" spans="1:21" ht="16">
+      <c r="U14" s="19" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="2:21">
+    <row r="15" spans="1:21">
       <c r="U15" s="14" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="2:21">
+    <row r="16" spans="1:21">
       <c r="U16" s="14" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="U14" r:id="rId1" xr:uid="{99704F72-9D01-1444-9468-4E615C52D4F3}"/>
+    <hyperlink ref="A1" location="Readme!B2" display="Home" xr:uid="{A10ABD49-F54B-3F4F-9C98-B2FBCA876EF8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98ED4665-8CA5-BC48-874C-AC7F75724267}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" customWidth="1"/>
-    <col min="3" max="3" width="79.83203125" customWidth="1"/>
-    <col min="4" max="4" width="97" customWidth="1"/>
+    <col min="1" max="1" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" customWidth="1"/>
+    <col min="4" max="4" width="79.83203125" customWidth="1"/>
+    <col min="5" max="5" width="97" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="26" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="68">
-      <c r="A2" s="2" t="s">
+    <row r="3" spans="1:5" ht="68">
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="51">
-      <c r="A3" t="s">
+    <row r="4" spans="1:5" ht="51">
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
+    <row r="5" spans="1:5">
+      <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D5" t="s">
         <v>13</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="136">
-      <c r="A5" s="2" t="s">
+    <row r="6" spans="1:5" ht="136">
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C6" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E6" t="s">
         <v>18</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Readme!B3" display="Home" xr:uid="{DBC6B468-142D-F248-8B30-E941A7468427}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1661C7ED-FEB2-6A4E-A2BB-13A4AD95C604}">
-  <dimension ref="B3:E7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="10.83203125" style="5"/>
     <col min="5" max="5" width="10.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5">
+    <row r="1" spans="1:5">
+      <c r="A1" s="26" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="B3" s="4"/>
       <c r="C3" s="3"/>
       <c r="E3" s="4"/>
     </row>
-    <row r="4" spans="2:5">
+    <row r="4" spans="1:5">
       <c r="B4" s="4"/>
       <c r="C4" s="3"/>
       <c r="E4" s="4"/>
     </row>
-    <row r="5" spans="2:5">
+    <row r="5" spans="1:5">
       <c r="B5" s="4">
         <v>3</v>
       </c>
@@ -1554,19 +1991,19 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:5">
+    <row r="6" spans="1:5">
       <c r="B6" s="4">
         <v>2</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="20"/>
+      <c r="D6" s="21"/>
       <c r="E6" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:5">
+    <row r="7" spans="1:5">
       <c r="B7" s="4">
         <v>1</v>
       </c>
@@ -1579,241 +2016,238 @@
   <mergeCells count="1">
     <mergeCell ref="C6:D6"/>
   </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Readme!B4" display="Home" xr:uid="{E2DA3DEC-9126-0A47-A0B9-C4DECD25C31E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6601D41D-AD5A-BE45-B683-D4A75B94E650}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="B1" s="7"/>
-      <c r="C1" s="12" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" s="26" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="C2" s="7"/>
+      <c r="D2" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="B2" s="7"/>
-      <c r="C2" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="7"/>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
-      <c r="G2" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>52</v>
+      <c r="G2" s="7"/>
+      <c r="H2" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="9" t="s">
-        <v>32</v>
+      <c r="K2" s="7"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="C3" s="7"/>
+      <c r="D3" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="7"/>
+      <c r="H3" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="B4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="B4" s="7"/>
-      <c r="C4" s="9" t="s">
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="C5" s="7"/>
+      <c r="D5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="9" t="s">
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="B5" s="7"/>
-      <c r="C5" s="9" t="s">
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="C6" s="7"/>
+      <c r="D6" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="B6" s="7"/>
-      <c r="C6" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
-      <c r="G6" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="9" t="s">
+        <v>40</v>
+      </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="B7" s="7"/>
-      <c r="C7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="7"/>
+      <c r="K6" s="7"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="C7" s="7"/>
+      <c r="D7" s="9" t="s">
+        <v>28</v>
+      </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
-      <c r="G7" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="9" t="s">
+        <v>43</v>
+      </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="B8" s="7"/>
+      <c r="K7" s="7"/>
+    </row>
+    <row r="8" spans="1:11">
       <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
+      <c r="D8" s="9" t="s">
+        <v>26</v>
+      </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
+      <c r="H8" s="9" t="s">
+        <v>48</v>
+      </c>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="B9" s="7"/>
-      <c r="C9" s="9" t="s">
-        <v>25</v>
-      </c>
+      <c r="K8" s="7"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="C9" s="7"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
-      <c r="G9" s="9" t="s">
-        <v>37</v>
-      </c>
+      <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="B10" s="7"/>
-      <c r="C10" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="7"/>
+      <c r="K9" s="7"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="C10" s="7"/>
+      <c r="D10" s="9" t="s">
+        <v>25</v>
+      </c>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="H10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="9" t="s">
+        <v>37</v>
+      </c>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="7"/>
+      <c r="K10" s="7"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="C11" s="7"/>
+      <c r="D11" s="9" t="s">
+        <v>27</v>
+      </c>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
-      <c r="G11" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="H11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="B12" s="7"/>
-      <c r="C12" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="7"/>
+      <c r="K11" s="7"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="B12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="9" t="s">
+        <v>31</v>
+      </c>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
-      <c r="G12" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="H12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="9" t="s">
+        <v>44</v>
+      </c>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="B13" s="7"/>
+      <c r="K12" s="7"/>
+    </row>
+    <row r="13" spans="1:11">
       <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
+      <c r="D13" s="12" t="s">
+        <v>45</v>
+      </c>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
-      <c r="G13" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="9" t="s">
+        <v>38</v>
+      </c>
       <c r="I13" s="7"/>
       <c r="J13" s="7"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="7"/>
+      <c r="K13" s="7"/>
+    </row>
+    <row r="14" spans="1:11">
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
-      <c r="G14" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="9" t="s">
+        <v>46</v>
+      </c>
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="B15" s="7"/>
+      <c r="K14" s="7"/>
+    </row>
+    <row r="15" spans="1:11">
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
+      <c r="H15" s="9" t="s">
+        <v>53</v>
+      </c>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="7"/>
+      <c r="K15" s="7"/>
+    </row>
+    <row r="16" spans="1:11">
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
@@ -1822,9 +2256,9 @@
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
-    </row>
-    <row r="17" spans="2:10">
-      <c r="B17" s="7"/>
+      <c r="K16" s="7"/>
+    </row>
+    <row r="17" spans="3:11">
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
@@ -1833,37 +2267,91 @@
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
-    </row>
-    <row r="18" spans="2:10">
-      <c r="D18" s="6" t="s">
+      <c r="K17" s="7"/>
+    </row>
+    <row r="18" spans="3:11">
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+    </row>
+    <row r="19" spans="3:11">
+      <c r="E19" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="I19" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:10">
-      <c r="D19" s="8" t="s">
+    <row r="20" spans="3:11">
+      <c r="E20" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8" t="s">
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="2:10">
-      <c r="B22" s="10" t="s">
+    <row r="23" spans="3:11">
+      <c r="C23" s="10" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="2:10">
-      <c r="B23" s="11" t="s">
+    <row r="24" spans="3:11">
+      <c r="C24" s="11" t="s">
         <v>50</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Readme!B5" display="Home" xr:uid="{B8A03DCC-1327-474B-872E-84C19038CF7E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3E9A9E8-FC63-8247-8005-D3F1CE187821}">
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="26" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="H6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="26">
+      <c r="C7" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="L7" s="27" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="H13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Readme!B6" display="Home" xr:uid="{F0FFEE55-B3D5-0646-A9BC-C8F80A47D613}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/doc/Java.xlsx
+++ b/doc/Java.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hades/Documents/GitHub/JavaAboutDemos/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF64B1D7-E75A-C44D-A4A1-7311FA4477FE}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4510B9-6707-7844-B783-BE44ECC971B8}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="460" windowWidth="27840" windowHeight="17540" activeTab="5" xr2:uid="{7C69AD57-AE32-C847-879F-875651E96C78}"/>
+    <workbookView xWindow="28800" yWindow="-1480" windowWidth="38400" windowHeight="24000" activeTab="6" xr2:uid="{7C69AD57-AE32-C847-879F-875651E96C78}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="6" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="LRU" sheetId="2" r:id="rId4"/>
     <sheet name="Java知识坐标系" sheetId="3" r:id="rId5"/>
     <sheet name="引用与对象" sheetId="5" r:id="rId6"/>
+    <sheet name="基本类型" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="121">
   <si>
     <t>Usage</t>
   </si>
@@ -311,12 +312,288 @@
     <t>操纵</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
+  <si>
+    <t>基本类型</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>最小值</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大值</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>包装器类型</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>byte</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>char</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>short</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>long</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>double</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>void</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boolean</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>8 bites = 1 byte</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>大小(1个字节等于8位)</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>\u0000' = Unicode 0</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Character</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>16 bites = 2 bytes</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Short</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Integer</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Long</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Float</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Double</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Void</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>\uFFFF' = Unicode 2</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线 (Body)"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线 (Body)"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线 (Body)"/>
+        <charset val="134"/>
+      </rPr>
+      <t>15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>-2</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="4"/>
+        <charset val="134"/>
+      </rPr>
+      <t>15</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>32 bites = 4 bytes</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线 (Body)"/>
+        <charset val="134"/>
+      </rPr>
+      <t>31</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>-2</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="4"/>
+        <charset val="134"/>
+      </rPr>
+      <t>31</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>64 bites = 8 bytes</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>-2</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="4"/>
+        <charset val="134"/>
+      </rPr>
+      <t>63</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="4"/>
+        <charset val="134"/>
+      </rPr>
+      <t>63</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>IEEE754</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>默认值</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="15">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -389,6 +666,41 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线 (Body)"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线 (Body)"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线 (Body)"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF232323"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -422,7 +734,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -502,13 +814,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -569,6 +896,28 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2355,4 +2704,206 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2B3760C-A0E5-9049-B5BD-1260B328E763}">
+  <dimension ref="B2:G18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" style="5"/>
+    <col min="2" max="2" width="10" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="10.83203125" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7">
+      <c r="B2" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" s="29" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7">
+      <c r="B3" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="G3" s="29"/>
+    </row>
+    <row r="4" spans="2:7">
+      <c r="B4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+    </row>
+    <row r="5" spans="2:7" ht="20">
+      <c r="B5" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="G5" s="29"/>
+    </row>
+    <row r="6" spans="2:7" ht="18">
+      <c r="B6" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="G6" s="29"/>
+    </row>
+    <row r="7" spans="2:7" ht="18">
+      <c r="B7" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="29"/>
+    </row>
+    <row r="8" spans="2:7" ht="18">
+      <c r="B8" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="G8" s="29"/>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="B9" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="G9" s="29"/>
+    </row>
+    <row r="10" spans="2:7">
+      <c r="B10" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="F10" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="G10" s="29"/>
+    </row>
+    <row r="11" spans="2:7">
+      <c r="B11" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="G11" s="29"/>
+    </row>
+    <row r="15" spans="2:7">
+      <c r="D15" s="36"/>
+    </row>
+    <row r="18" spans="4:4" ht="18">
+      <c r="D18" s="35"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/doc/Java.xlsx
+++ b/doc/Java.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hades/Documents/GitHub/JavaAboutDemos/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4510B9-6707-7844-B783-BE44ECC971B8}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F51DE6A1-2885-524C-B125-B049A3E16C30}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28800" yWindow="-1480" windowWidth="38400" windowHeight="24000" activeTab="6" xr2:uid="{7C69AD57-AE32-C847-879F-875651E96C78}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="130">
   <si>
     <t>Usage</t>
   </si>
@@ -311,6 +311,9 @@
   <si>
     <t>操纵</t>
     <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本类型</t>
   </si>
   <si>
     <t>基本类型</t>
@@ -586,6 +589,84 @@
   </si>
   <si>
     <t>默认值</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>-2</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="4"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>= -128</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="4"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1 = 127</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Byte</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0f</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0d</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>false</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BigInteger</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BigDecimal</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1864,7 +1945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DB7D6FA-3CC5-D149-87C6-B74F2C3A7F2D}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="25.33203125" bestFit="1" customWidth="1"/>
@@ -1919,6 +2000,14 @@
         <v>78</v>
       </c>
     </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <hyperlinks>
@@ -1927,6 +2016,7 @@
     <hyperlink ref="B4" location="LRU!A1" display="LRU" xr:uid="{A09283A5-69D6-CA40-964D-B15873694DBF}"/>
     <hyperlink ref="B5" location="Java知识坐标系!A1" display="Java知识坐标系" xr:uid="{87E8B54B-C023-8741-BABD-4BA61CF4F9AB}"/>
     <hyperlink ref="B6" location="引用与对象!A1" display="引用与对象" xr:uid="{ED9556B9-9183-3049-9D57-16682A24BDD4}"/>
+    <hyperlink ref="B7" location="基本类型!A1" display="基本类型" xr:uid="{DF87A86A-8938-B244-9BB8-A1A29E200822}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2708,7 +2798,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2B3760C-A0E5-9049-B5BD-1260B328E763}">
-  <dimension ref="B2:G18"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="5"/>
@@ -2717,186 +2807,256 @@
     <col min="4" max="4" width="20.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.83203125" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.1640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="10.83203125" style="5"/>
+    <col min="7" max="7" width="20.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="10.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7">
+    <row r="1" spans="1:7">
+      <c r="A1" s="26" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="B2" s="30" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="G2" s="29" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="B3" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="G3" s="31" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18">
+      <c r="B4" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="D2" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="E2" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="F2" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="G2" s="29" t="s">
+      <c r="D4" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="G4" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="20">
+      <c r="B5" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18">
+      <c r="B6" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="G6" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18">
+      <c r="B7" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="G7" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="18">
+      <c r="B8" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="G8" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="B9" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" s="34" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="3" spans="2:7">
-      <c r="B3" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="C3" s="29" t="s">
+      <c r="E9" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="B10" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="F10" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="G10" s="29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="B11" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="D3" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="E3" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="F3" s="29" t="s">
+      <c r="C11" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="G3" s="29"/>
-    </row>
-    <row r="4" spans="2:7">
-      <c r="B4" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="C4" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-    </row>
-    <row r="5" spans="2:7" ht="20">
-      <c r="B5" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="D5" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="E5" s="33" t="s">
+      <c r="D11" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="F11" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="F5" s="29" t="s">
-        <v>101</v>
-      </c>
-      <c r="G5" s="29"/>
-    </row>
-    <row r="6" spans="2:7" ht="18">
-      <c r="B6" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="F6" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="G6" s="29"/>
-    </row>
-    <row r="7" spans="2:7" ht="18">
-      <c r="B7" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="C7" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>115</v>
-      </c>
-      <c r="E7" s="29" t="s">
-        <v>114</v>
-      </c>
-      <c r="F7" s="29" t="s">
-        <v>104</v>
-      </c>
-      <c r="G7" s="29"/>
-    </row>
-    <row r="8" spans="2:7" ht="18">
-      <c r="B8" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>117</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="F8" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="G8" s="29"/>
-    </row>
-    <row r="9" spans="2:7">
-      <c r="B9" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="F9" s="29" t="s">
-        <v>107</v>
-      </c>
-      <c r="G9" s="29"/>
-    </row>
-    <row r="10" spans="2:7">
-      <c r="B10" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D10" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="F10" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="G10" s="29"/>
-    </row>
-    <row r="11" spans="2:7">
-      <c r="B11" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="C11" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="E11" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="F11" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="G11" s="29"/>
-    </row>
-    <row r="15" spans="2:7">
+      <c r="G11" s="29" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="B12" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="E12" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="G12" s="29" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="B13" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="F13" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="G13" s="29" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="D15" s="36"/>
     </row>
     <row r="18" spans="4:4" ht="18">
@@ -2904,6 +3064,9 @@
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Readme!B7" display="Home" xr:uid="{4490E64E-64DC-BE47-8559-B7ECE961060E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/doc/Java.xlsx
+++ b/doc/Java.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hades/Documents/GitHub/JavaAboutDemos/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F51DE6A1-2885-524C-B125-B049A3E16C30}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C500B8B-C401-DF40-8575-2CA7DAAD2C8B}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28800" yWindow="-1480" windowWidth="38400" windowHeight="24000" activeTab="6" xr2:uid="{7C69AD57-AE32-C847-879F-875651E96C78}"/>
   </bookViews>

--- a/doc/Java.xlsx
+++ b/doc/Java.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11208"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hades/Documents/GitHub/JavaAboutDemos/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C500B8B-C401-DF40-8575-2CA7DAAD2C8B}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27CA1108-B619-A94C-B3BA-568287839BBD}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="-1480" windowWidth="38400" windowHeight="24000" activeTab="6" xr2:uid="{7C69AD57-AE32-C847-879F-875651E96C78}"/>
+    <workbookView xWindow="28800" yWindow="-1020" windowWidth="38400" windowHeight="23540" activeTab="7" xr2:uid="{7C69AD57-AE32-C847-879F-875651E96C78}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="6" r:id="rId1"/>
@@ -20,8 +20,9 @@
     <sheet name="Java知识坐标系" sheetId="3" r:id="rId5"/>
     <sheet name="引用与对象" sheetId="5" r:id="rId6"/>
     <sheet name="基本类型" sheetId="7" r:id="rId7"/>
+    <sheet name="正负数的二进制表示" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="142">
   <si>
     <t>Usage</t>
   </si>
@@ -667,6 +668,53 @@
   </si>
   <si>
     <t>BigDecimal</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>正负数的二进制表示</t>
+  </si>
+  <si>
+    <t>正负数的二进制表示</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>int a = 1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>int b = -1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>原码</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>反码</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>实际上是32位，为了简单写成8位</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>规则：补码 取反 + 1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>规则：原码 取反 + 1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>补码 =&gt; -1</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1 =&gt; 补码</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>补码（二进制形式存储）</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -916,7 +964,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -957,12 +1005,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1000,6 +1042,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1945,7 +2007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DB7D6FA-3CC5-D149-87C6-B74F2C3A7F2D}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="25.33203125" bestFit="1" customWidth="1"/>
@@ -1953,10 +2015,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="21" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1964,7 +2026,7 @@
       <c r="A2" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="22" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1972,7 +2034,7 @@
       <c r="A3" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="22" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1980,7 +2042,7 @@
       <c r="A4" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="22" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1988,7 +2050,7 @@
       <c r="A5" t="s">
         <v>77</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="22" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1996,7 +2058,7 @@
       <c r="A6" t="s">
         <v>79</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2004,8 +2066,16 @@
       <c r="A7" t="s">
         <v>85</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="22" t="s">
         <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2017,6 +2087,7 @@
     <hyperlink ref="B5" location="Java知识坐标系!A1" display="Java知识坐标系" xr:uid="{87E8B54B-C023-8741-BABD-4BA61CF4F9AB}"/>
     <hyperlink ref="B6" location="引用与对象!A1" display="引用与对象" xr:uid="{ED9556B9-9183-3049-9D57-16682A24BDD4}"/>
     <hyperlink ref="B7" location="基本类型!A1" display="基本类型" xr:uid="{DF87A86A-8938-B244-9BB8-A1A29E200822}"/>
+    <hyperlink ref="B8" location="正负数的二进制表示!A1" display="正负数的二进制表示" xr:uid="{9C978E4B-665F-8546-BD98-D1E57484D9F2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2038,12 +2109,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="16">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="23" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:21">
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="20" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2314,7 +2385,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="24" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2407,7 +2478,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="24" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2434,10 +2505,10 @@
       <c r="B6" s="4">
         <v>2</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="21"/>
+      <c r="D6" s="36"/>
       <c r="E6" s="4">
         <v>3</v>
       </c>
@@ -2470,7 +2541,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="24" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2764,7 +2835,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="24" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2774,10 +2845,10 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="26">
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="L7" s="27" t="s">
+      <c r="L7" s="25" t="s">
         <v>81</v>
       </c>
     </row>
@@ -2812,255 +2883,255 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="24" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="G2" s="27" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="E3" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="29" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18">
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="G4" s="29">
+      <c r="G4" s="27">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="20">
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="G5" s="29" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18">
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="F6" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="G6" s="29">
+      <c r="G6" s="27">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18">
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="F7" s="29" t="s">
+      <c r="F7" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="27">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="18">
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="27">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="34" t="s">
+      <c r="D9" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="E9" s="34" t="s">
+      <c r="E9" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="F9" s="29" t="s">
+      <c r="F9" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="G9" s="29" t="s">
+      <c r="G9" s="27" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="D10" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="E10" s="34" t="s">
+      <c r="E10" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="F10" s="29" t="s">
+      <c r="F10" s="27" t="s">
         <v>109</v>
       </c>
-      <c r="G10" s="29" t="s">
+      <c r="G10" s="27" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="D11" s="29" t="s">
+      <c r="D11" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="E11" s="29" t="s">
+      <c r="E11" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="F11" s="29" t="s">
+      <c r="F11" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="G11" s="29" t="s">
+      <c r="G11" s="27" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="29" t="s">
+      <c r="D12" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="E12" s="29" t="s">
+      <c r="E12" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="F12" s="29" t="s">
+      <c r="F12" s="27" t="s">
         <v>128</v>
       </c>
-      <c r="G12" s="29" t="s">
+      <c r="G12" s="27" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="D13" s="29" t="s">
+      <c r="D13" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="E13" s="29" t="s">
+      <c r="E13" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="F13" s="29" t="s">
+      <c r="F13" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="G13" s="29" t="s">
+      <c r="G13" s="27" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="D15" s="36"/>
+      <c r="D15" s="34"/>
     </row>
     <row r="18" spans="4:4" ht="18">
-      <c r="D18" s="35"/>
+      <c r="D18" s="33"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -3069,4 +3140,311 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D156AB3-8544-8C4D-94EE-29262FA46ED8}">
+  <dimension ref="A1:Q20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="3" max="3" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="13" width="2.83203125" style="5" customWidth="1"/>
+    <col min="14" max="16" width="2.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="A1" s="24" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="C2" s="37"/>
+      <c r="F2" s="41" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="C3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="C4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F4" s="27">
+        <v>0</v>
+      </c>
+      <c r="G4" s="27">
+        <v>0</v>
+      </c>
+      <c r="H4" s="27">
+        <v>0</v>
+      </c>
+      <c r="I4" s="27">
+        <v>0</v>
+      </c>
+      <c r="J4" s="27">
+        <v>0</v>
+      </c>
+      <c r="K4" s="27">
+        <v>0</v>
+      </c>
+      <c r="L4" s="27">
+        <v>0</v>
+      </c>
+      <c r="M4" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="C5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F5" s="27">
+        <v>0</v>
+      </c>
+      <c r="G5" s="27">
+        <v>0</v>
+      </c>
+      <c r="H5" s="27">
+        <v>0</v>
+      </c>
+      <c r="I5" s="27">
+        <v>0</v>
+      </c>
+      <c r="J5" s="27">
+        <v>0</v>
+      </c>
+      <c r="K5" s="27">
+        <v>0</v>
+      </c>
+      <c r="L5" s="27">
+        <v>0</v>
+      </c>
+      <c r="M5" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="C6" t="s">
+        <v>141</v>
+      </c>
+      <c r="F6" s="27">
+        <v>0</v>
+      </c>
+      <c r="G6" s="27">
+        <v>0</v>
+      </c>
+      <c r="H6" s="27">
+        <v>0</v>
+      </c>
+      <c r="I6" s="27">
+        <v>0</v>
+      </c>
+      <c r="J6" s="27">
+        <v>0</v>
+      </c>
+      <c r="K6" s="27">
+        <v>0</v>
+      </c>
+      <c r="L6" s="27">
+        <v>0</v>
+      </c>
+      <c r="M6" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="C12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="C13" s="39" t="s">
+        <v>140</v>
+      </c>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="40"/>
+      <c r="N13" s="42"/>
+      <c r="O13" s="42"/>
+      <c r="P13" s="42"/>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="C14" t="s">
+        <v>134</v>
+      </c>
+      <c r="F14" s="27">
+        <v>1</v>
+      </c>
+      <c r="G14" s="27">
+        <v>0</v>
+      </c>
+      <c r="H14" s="27">
+        <v>0</v>
+      </c>
+      <c r="I14" s="27">
+        <v>0</v>
+      </c>
+      <c r="J14" s="27">
+        <v>0</v>
+      </c>
+      <c r="K14" s="27">
+        <v>0</v>
+      </c>
+      <c r="L14" s="27">
+        <v>0</v>
+      </c>
+      <c r="M14" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="C15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F15" s="27">
+        <v>1</v>
+      </c>
+      <c r="G15" s="38">
+        <v>1</v>
+      </c>
+      <c r="H15" s="38">
+        <v>1</v>
+      </c>
+      <c r="I15" s="38">
+        <v>1</v>
+      </c>
+      <c r="J15" s="38">
+        <v>1</v>
+      </c>
+      <c r="K15" s="38">
+        <v>1</v>
+      </c>
+      <c r="L15" s="38">
+        <v>1</v>
+      </c>
+      <c r="M15" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="C16" t="s">
+        <v>141</v>
+      </c>
+      <c r="F16" s="27">
+        <v>1</v>
+      </c>
+      <c r="G16" s="38">
+        <v>1</v>
+      </c>
+      <c r="H16" s="38">
+        <v>1</v>
+      </c>
+      <c r="I16" s="38">
+        <v>1</v>
+      </c>
+      <c r="J16" s="38">
+        <v>1</v>
+      </c>
+      <c r="K16" s="38">
+        <v>1</v>
+      </c>
+      <c r="L16" s="38">
+        <v>1</v>
+      </c>
+      <c r="M16" s="38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17">
+      <c r="C18" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="41" t="s">
+        <v>137</v>
+      </c>
+      <c r="G18" s="40"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="40"/>
+      <c r="L18" s="40"/>
+      <c r="M18" s="40"/>
+      <c r="N18" s="42"/>
+      <c r="O18" s="42"/>
+      <c r="P18" s="42"/>
+      <c r="Q18" s="42"/>
+    </row>
+    <row r="19" spans="3:17">
+      <c r="F19" s="27">
+        <v>1</v>
+      </c>
+      <c r="G19" s="38">
+        <v>0</v>
+      </c>
+      <c r="H19" s="38">
+        <v>0</v>
+      </c>
+      <c r="I19" s="38">
+        <v>0</v>
+      </c>
+      <c r="J19" s="38">
+        <v>0</v>
+      </c>
+      <c r="K19" s="38">
+        <v>0</v>
+      </c>
+      <c r="L19" s="38">
+        <v>0</v>
+      </c>
+      <c r="M19" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="3:17">
+      <c r="F20" s="27">
+        <v>1</v>
+      </c>
+      <c r="G20" s="38">
+        <v>0</v>
+      </c>
+      <c r="H20" s="38">
+        <v>0</v>
+      </c>
+      <c r="I20" s="38">
+        <v>0</v>
+      </c>
+      <c r="J20" s="38">
+        <v>0</v>
+      </c>
+      <c r="K20" s="38">
+        <v>0</v>
+      </c>
+      <c r="L20" s="38">
+        <v>0</v>
+      </c>
+      <c r="M20" s="38">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Readme!B8" display="Home" xr:uid="{0F392486-6D06-E248-90AE-31545A5A02A2}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/doc/Java.xlsx
+++ b/doc/Java.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hades/Documents/GitHub/JavaAboutDemos/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27CA1108-B619-A94C-B3BA-568287839BBD}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C5D81C-4D93-2843-AE5A-E30F69C8A4B5}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28800" yWindow="-1020" windowWidth="38400" windowHeight="23540" activeTab="7" xr2:uid="{7C69AD57-AE32-C847-879F-875651E96C78}"/>
   </bookViews>

--- a/doc/Java.xlsx
+++ b/doc/Java.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hades/Documents/GitHub/JavaAboutDemos/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C5D81C-4D93-2843-AE5A-E30F69C8A4B5}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8BB7C0-3EEF-7B40-AAE5-0987F8A2B93D}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="-1020" windowWidth="38400" windowHeight="23540" activeTab="7" xr2:uid="{7C69AD57-AE32-C847-879F-875651E96C78}"/>
+    <workbookView xWindow="960" yWindow="460" windowWidth="27840" windowHeight="17540" xr2:uid="{7C69AD57-AE32-C847-879F-875651E96C78}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="6" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="引用与对象" sheetId="5" r:id="rId6"/>
     <sheet name="基本类型" sheetId="7" r:id="rId7"/>
     <sheet name="正负数的二进制表示" sheetId="8" r:id="rId8"/>
+    <sheet name="涉及基本类型的重载" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="144">
   <si>
     <t>Usage</t>
   </si>
@@ -440,7 +441,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="等线 (Body)"/>
-        <charset val="134"/>
       </rPr>
       <t>-1</t>
     </r>
@@ -456,7 +456,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="等线 (Body)"/>
-        <charset val="134"/>
       </rPr>
       <t>15</t>
     </r>
@@ -503,7 +502,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="等线 (Body)"/>
-        <charset val="134"/>
       </rPr>
       <t>31</t>
     </r>
@@ -715,6 +713,13 @@
   </si>
   <si>
     <t>补码（二进制形式存储）</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>涉及基本类型的重载</t>
+  </si>
+  <si>
+    <t>涉及基本类型的重载</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -808,13 +813,11 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="等线 (Body)"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="等线 (Body)"/>
-      <charset val="134"/>
     </font>
     <font>
       <vertAlign val="superscript"/>
@@ -863,7 +866,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -958,13 +961,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1042,12 +1060,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1062,6 +1074,15 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1710,6 +1731,329 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>736600</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Arrow Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9073B21-D1B7-2B43-9D71-037A9C759BFB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2565400" y="1143000"/>
+          <a:ext cx="647700" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>736600</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Straight Arrow Connector 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E96448D5-DA65-6649-B1BB-4AEBE1DB4B9E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4216400" y="1117600"/>
+          <a:ext cx="647700" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>736600</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="Straight Arrow Connector 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97402834-2D96-DE49-8257-1DA1E25EB8CD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5867400" y="1143000"/>
+          <a:ext cx="647700" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>723900</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="Straight Arrow Connector 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07B76E39-04AB-F842-855E-140960171E3E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7505700" y="1130300"/>
+          <a:ext cx="647700" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>736600</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="Straight Arrow Connector 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD1C5D80-A2CC-0645-BD54-82E9FA75CABE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9169400" y="1130300"/>
+          <a:ext cx="647700" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="Straight Arrow Connector 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C8C3247-DC61-BC4F-87B5-711E5836B623}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="4191000" y="1346200"/>
+          <a:ext cx="952500" cy="609600"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2007,7 +2351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DB7D6FA-3CC5-D149-87C6-B74F2C3A7F2D}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="25.33203125" bestFit="1" customWidth="1"/>
@@ -2076,6 +2420,14 @@
       </c>
       <c r="B8" s="22" t="s">
         <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -2088,6 +2440,7 @@
     <hyperlink ref="B6" location="引用与对象!A1" display="引用与对象" xr:uid="{ED9556B9-9183-3049-9D57-16682A24BDD4}"/>
     <hyperlink ref="B7" location="基本类型!A1" display="基本类型" xr:uid="{DF87A86A-8938-B244-9BB8-A1A29E200822}"/>
     <hyperlink ref="B8" location="正负数的二进制表示!A1" display="正负数的二进制表示" xr:uid="{9C978E4B-665F-8546-BD98-D1E57484D9F2}"/>
+    <hyperlink ref="B9" location="涉及基本类型的重载!A1" display="涉及基本类型的重载" xr:uid="{691F2B36-D51B-4447-AC80-C24BFBDB990F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2505,10 +2858,10 @@
       <c r="B6" s="4">
         <v>2</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C6" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="36"/>
+      <c r="D6" s="42"/>
       <c r="E6" s="4">
         <v>3</v>
       </c>
@@ -2947,7 +3300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="20">
+    <row r="5" spans="1:7" ht="19">
       <c r="B5" s="27" t="s">
         <v>91</v>
       </c>
@@ -3158,8 +3511,8 @@
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="C2" s="37"/>
-      <c r="F2" s="41" t="s">
+      <c r="C2" s="35"/>
+      <c r="F2" s="39" t="s">
         <v>136</v>
       </c>
     </row>
@@ -3261,24 +3614,24 @@
       </c>
     </row>
     <row r="13" spans="1:16">
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="37" t="s">
         <v>140</v>
       </c>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="41" t="s">
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="39" t="s">
         <v>138</v>
       </c>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="40"/>
-      <c r="K13" s="40"/>
-      <c r="L13" s="40"/>
-      <c r="M13" s="40"/>
-      <c r="N13" s="42"/>
-      <c r="O13" s="42"/>
-      <c r="P13" s="42"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="L13" s="38"/>
+      <c r="M13" s="38"/>
+      <c r="N13" s="40"/>
+      <c r="O13" s="40"/>
+      <c r="P13" s="40"/>
     </row>
     <row r="14" spans="1:16">
       <c r="C14" t="s">
@@ -3316,25 +3669,25 @@
       <c r="F15" s="27">
         <v>1</v>
       </c>
-      <c r="G15" s="38">
-        <v>1</v>
-      </c>
-      <c r="H15" s="38">
-        <v>1</v>
-      </c>
-      <c r="I15" s="38">
-        <v>1</v>
-      </c>
-      <c r="J15" s="38">
-        <v>1</v>
-      </c>
-      <c r="K15" s="38">
-        <v>1</v>
-      </c>
-      <c r="L15" s="38">
-        <v>1</v>
-      </c>
-      <c r="M15" s="38">
+      <c r="G15" s="36">
+        <v>1</v>
+      </c>
+      <c r="H15" s="36">
+        <v>1</v>
+      </c>
+      <c r="I15" s="36">
+        <v>1</v>
+      </c>
+      <c r="J15" s="36">
+        <v>1</v>
+      </c>
+      <c r="K15" s="36">
+        <v>1</v>
+      </c>
+      <c r="L15" s="36">
+        <v>1</v>
+      </c>
+      <c r="M15" s="36">
         <v>0</v>
       </c>
     </row>
@@ -3345,72 +3698,72 @@
       <c r="F16" s="27">
         <v>1</v>
       </c>
-      <c r="G16" s="38">
-        <v>1</v>
-      </c>
-      <c r="H16" s="38">
-        <v>1</v>
-      </c>
-      <c r="I16" s="38">
-        <v>1</v>
-      </c>
-      <c r="J16" s="38">
-        <v>1</v>
-      </c>
-      <c r="K16" s="38">
-        <v>1</v>
-      </c>
-      <c r="L16" s="38">
-        <v>1</v>
-      </c>
-      <c r="M16" s="38">
+      <c r="G16" s="36">
+        <v>1</v>
+      </c>
+      <c r="H16" s="36">
+        <v>1</v>
+      </c>
+      <c r="I16" s="36">
+        <v>1</v>
+      </c>
+      <c r="J16" s="36">
+        <v>1</v>
+      </c>
+      <c r="K16" s="36">
+        <v>1</v>
+      </c>
+      <c r="L16" s="36">
+        <v>1</v>
+      </c>
+      <c r="M16" s="36">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="3:17">
-      <c r="C18" s="39" t="s">
+      <c r="C18" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="41" t="s">
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="G18" s="40"/>
-      <c r="H18" s="40"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="40"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="40"/>
-      <c r="M18" s="40"/>
-      <c r="N18" s="42"/>
-      <c r="O18" s="42"/>
-      <c r="P18" s="42"/>
-      <c r="Q18" s="42"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="38"/>
+      <c r="L18" s="38"/>
+      <c r="M18" s="38"/>
+      <c r="N18" s="40"/>
+      <c r="O18" s="40"/>
+      <c r="P18" s="40"/>
+      <c r="Q18" s="40"/>
     </row>
     <row r="19" spans="3:17">
       <c r="F19" s="27">
         <v>1</v>
       </c>
-      <c r="G19" s="38">
-        <v>0</v>
-      </c>
-      <c r="H19" s="38">
-        <v>0</v>
-      </c>
-      <c r="I19" s="38">
-        <v>0</v>
-      </c>
-      <c r="J19" s="38">
-        <v>0</v>
-      </c>
-      <c r="K19" s="38">
-        <v>0</v>
-      </c>
-      <c r="L19" s="38">
-        <v>0</v>
-      </c>
-      <c r="M19" s="38">
+      <c r="G19" s="36">
+        <v>0</v>
+      </c>
+      <c r="H19" s="36">
+        <v>0</v>
+      </c>
+      <c r="I19" s="36">
+        <v>0</v>
+      </c>
+      <c r="J19" s="36">
+        <v>0</v>
+      </c>
+      <c r="K19" s="36">
+        <v>0</v>
+      </c>
+      <c r="L19" s="36">
+        <v>0</v>
+      </c>
+      <c r="M19" s="36">
         <v>0</v>
       </c>
     </row>
@@ -3418,25 +3771,25 @@
       <c r="F20" s="27">
         <v>1</v>
       </c>
-      <c r="G20" s="38">
-        <v>0</v>
-      </c>
-      <c r="H20" s="38">
-        <v>0</v>
-      </c>
-      <c r="I20" s="38">
-        <v>0</v>
-      </c>
-      <c r="J20" s="38">
-        <v>0</v>
-      </c>
-      <c r="K20" s="38">
-        <v>0</v>
-      </c>
-      <c r="L20" s="38">
-        <v>0</v>
-      </c>
-      <c r="M20" s="38">
+      <c r="G20" s="36">
+        <v>0</v>
+      </c>
+      <c r="H20" s="36">
+        <v>0</v>
+      </c>
+      <c r="I20" s="36">
+        <v>0</v>
+      </c>
+      <c r="J20" s="36">
+        <v>0</v>
+      </c>
+      <c r="K20" s="36">
+        <v>0</v>
+      </c>
+      <c r="L20" s="36">
+        <v>0</v>
+      </c>
+      <c r="M20" s="36">
         <v>1</v>
       </c>
     </row>
@@ -3447,4 +3800,54 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C637C90-A893-BB40-AAA3-2A0BB6F74270}">
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="16384" width="10.83203125" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="23" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="17" thickBot="1"/>
+    <row r="6" spans="1:13" ht="17" thickBot="1">
+      <c r="C6" s="43" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="G6" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="I6" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="K6" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="M6" s="43" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="17" thickBot="1"/>
+    <row r="10" spans="1:13" ht="17" thickBot="1">
+      <c r="E10" s="43" t="s">
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Readme!B9" display="Home" xr:uid="{599FE74C-C684-204C-80F1-34B351331EF5}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>